--- a/02_DIA_inicio_2026_analisis_assets/rbd_9586_liceo-araucania_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9586_liceo-araucania_nt2_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0327E4F5-2A01-4C9D-A64A-DA6A091348C2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89D47E3A-D6F6-4771-B8B0-810606239DE8}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{69428523-5C35-4579-9F27-74BE689AEBD2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{727FB9D4-994D-4660-AC34-A0F99D26F61E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{316ED48F-7C2E-47B2-BEB9-73002F0306AB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{729F07D5-5A39-4299-B43E-3F08AA002BEB}"/>
 </file>